--- a/design/tables/Level.xlsx
+++ b/design/tables/Level.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="R54be27ce915e400e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="R617ff920f02345aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +17,7 @@
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="0.######"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -33,8 +33,19 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF24453D"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -51,6 +62,16 @@
         <x:fgColor rgb="FF34564C"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5EDE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF335A50"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -58,7 +79,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -82,6 +103,16 @@
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -293,9 +324,10 @@
     <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="27.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="48" customHeight="1">
+    <x:row r="1" ht="54" customHeight="1">
       <x:c r="A1" s="6" t="str">
         <x:v>唯一ID，不可重复</x:v>
       </x:c>
@@ -322,6 +354,9 @@
       </x:c>
       <x:c r="I1" s="6" t="str">
         <x:v>可用店员（竖线分隔）</x:v>
+      </x:c>
+      <x:c r="J1" s="12" t="str">
+        <x:v>adventure冒险；challenge固定挑战；不计入冒险进度</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
@@ -352,6 +387,9 @@
       <x:c r="I2" s="3" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="J2" s="12" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -381,6 +419,9 @@
       <x:c r="I3" s="3" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="J3" s="12" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -410,6 +451,9 @@
       <x:c r="I4" s="6" t="str">
         <x:v>可用店员（竖线分隔）</x:v>
       </x:c>
+      <x:c r="J4" s="12" t="str">
+        <x:v>模式</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -439,6 +483,9 @@
       <x:c r="I5" s="5" t="str">
         <x:v>availableTowers</x:v>
       </x:c>
+      <x:c r="J5" s="14" t="str">
+        <x:v>mode</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="n">
@@ -452,19 +499,22 @@
       </x:c>
       <x:c r="D6" s="2" t="str"/>
       <x:c r="E6" s="7" t="n">
-        <x:v>170</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F6" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G6" s="8" t="n">
-        <x:v>0.9</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="H6" s="8" t="n">
-        <x:v>0.88</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="2" t="str">
         <x:v>sprout</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -479,19 +529,22 @@
       </x:c>
       <x:c r="D7" s="2" t="str"/>
       <x:c r="E7" s="7" t="n">
-        <x:v>210</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="F7" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G7" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="H7" s="8" t="n">
-        <x:v>1.02</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I7" s="2" t="str">
         <x:v>sprout|frost</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -506,19 +559,22 @@
       </x:c>
       <x:c r="D8" s="2" t="str"/>
       <x:c r="E8" s="7" t="n">
-        <x:v>250</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="F8" s="7" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G8" s="8" t="n">
-        <x:v>1.06</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="H8" s="8" t="n">
-        <x:v>1.02</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I8" s="2" t="str">
         <x:v>sprout|frost|bloom</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -536,16 +592,19 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="F9" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G9" s="8" t="n">
         <x:v>1.12</x:v>
       </x:c>
       <x:c r="H9" s="8" t="n">
-        <x:v>1.03</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I9" s="2" t="str">
         <x:v>sprout|frost|bloom</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -565,16 +624,19 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="F10" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G10" s="8" t="n">
         <x:v>1.16</x:v>
       </x:c>
       <x:c r="H10" s="8" t="n">
-        <x:v>1.04</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I10" s="2" t="str">
         <x:v>sprout|frost|bloom</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -594,16 +656,19 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="F11" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G11" s="8" t="n">
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="H11" s="8" t="n">
-        <x:v>1.08</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="2" t="str">
         <x:v>sprout|frost|bloom|scope</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -623,16 +688,19 @@
         <x:v>310</x:v>
       </x:c>
       <x:c r="F12" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G12" s="8" t="n">
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="H12" s="8" t="n">
-        <x:v>1.1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="2" t="str">
         <x:v>sprout|frost|bloom|scope</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -652,16 +720,19 @@
         <x:v>320</x:v>
       </x:c>
       <x:c r="F13" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G13" s="8" t="n">
         <x:v>1.38</x:v>
       </x:c>
       <x:c r="H13" s="8" t="n">
-        <x:v>1.12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I13" s="2" t="str">
         <x:v>scope|frost|bloom|spark</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -681,17 +752,20 @@
         <x:v>330</x:v>
       </x:c>
       <x:c r="F14" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G14" s="8" t="n">
         <x:v>1.46</x:v>
       </x:c>
       <x:c r="H14" s="8" t="n">
-        <x:v>1.15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="2" t="str">
         <x:v>scope|frost|bloom|spark</x:v>
       </x:c>
+      <x:c r="J14" t="str">
+        <x:v>adventure</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="7" t="n">
@@ -710,16 +784,19 @@
         <x:v>370</x:v>
       </x:c>
       <x:c r="F15" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G15" s="8" t="n">
         <x:v>1.54</x:v>
       </x:c>
       <x:c r="H15" s="8" t="n">
-        <x:v>1.18</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="2" t="str">
         <x:v>scope|frost|bloom|spark</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -739,16 +816,19 @@
         <x:v>330</x:v>
       </x:c>
       <x:c r="F16" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G16" s="8" t="n">
         <x:v>1.48</x:v>
       </x:c>
       <x:c r="H16" s="8" t="n">
-        <x:v>1.12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="2" t="str">
         <x:v>sprout|frost|bloom|ember</x:v>
+      </x:c>
+      <x:c r="J16" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -768,16 +848,19 @@
         <x:v>338</x:v>
       </x:c>
       <x:c r="F17" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G17" s="8" t="n">
         <x:v>1.525</x:v>
       </x:c>
       <x:c r="H17" s="8" t="n">
-        <x:v>1.132</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I17" s="2" t="str">
         <x:v>scope|frost|bloom|ember</x:v>
+      </x:c>
+      <x:c r="J17" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
@@ -797,16 +880,19 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="F18" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G18" s="8" t="n">
         <x:v>1.57</x:v>
       </x:c>
       <x:c r="H18" s="8" t="n">
-        <x:v>1.144</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I18" s="2" t="str">
         <x:v>sprout|bloom|mint|ember</x:v>
+      </x:c>
+      <x:c r="J18" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -826,16 +912,19 @@
         <x:v>354</x:v>
       </x:c>
       <x:c r="F19" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G19" s="8" t="n">
         <x:v>1.615</x:v>
       </x:c>
       <x:c r="H19" s="8" t="n">
-        <x:v>1.156</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="2" t="str">
         <x:v>scope|spark|mint|frost</x:v>
+      </x:c>
+      <x:c r="J19" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -855,16 +944,19 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="F20" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G20" s="8" t="n">
         <x:v>1.66</x:v>
       </x:c>
       <x:c r="H20" s="8" t="n">
-        <x:v>1.168</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="2" t="str">
         <x:v>scope|bloom|ember|mint</x:v>
+      </x:c>
+      <x:c r="J20" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -881,19 +973,22 @@
         <x:v>level.16.goal</x:v>
       </x:c>
       <x:c r="E21" s="7" t="n">
-        <x:v>370</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="F21" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G21" s="8" t="n">
         <x:v>1.705</x:v>
       </x:c>
       <x:c r="H21" s="8" t="n">
-        <x:v>1.18</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="2" t="str">
         <x:v>sprout|frost|bloom|fan</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -910,19 +1005,22 @@
         <x:v>level.17.goal</x:v>
       </x:c>
       <x:c r="E22" s="7" t="n">
-        <x:v>378</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="F22" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G22" s="8" t="n">
         <x:v>1.75</x:v>
       </x:c>
       <x:c r="H22" s="8" t="n">
-        <x:v>1.192</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="2" t="str">
         <x:v>scope|spark|frost|fan</x:v>
+      </x:c>
+      <x:c r="J22" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -942,16 +1040,19 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="F23" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G23" s="8" t="n">
         <x:v>1.795</x:v>
       </x:c>
       <x:c r="H23" s="8" t="n">
-        <x:v>1.204</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="2" t="str">
         <x:v>scope|bloom|mint|fan</x:v>
+      </x:c>
+      <x:c r="J23" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -971,16 +1072,19 @@
         <x:v>394</x:v>
       </x:c>
       <x:c r="F24" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G24" s="8" t="n">
         <x:v>1.84</x:v>
       </x:c>
       <x:c r="H24" s="8" t="n">
-        <x:v>1.216</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="2" t="str">
         <x:v>scope|frost|ember|fan</x:v>
+      </x:c>
+      <x:c r="J24" t="str">
+        <x:v>adventure</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -1000,16 +1104,51 @@
         <x:v>402</x:v>
       </x:c>
       <x:c r="F25" s="7" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G25" s="8" t="n">
         <x:v>1.885</x:v>
       </x:c>
       <x:c r="H25" s="8" t="n">
-        <x:v>1.228</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I25" s="2" t="str">
         <x:v>scope|frost|bloom|mint</x:v>
+      </x:c>
+      <x:c r="J25" t="str">
+        <x:v>adventure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B26" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>challenge.title</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>challenge.goal</x:v>
+      </x:c>
+      <x:c r="E26" t="n">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="F26" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I26" t="str">
+        <x:v>frost|bloom|scope|mint</x:v>
+      </x:c>
+      <x:c r="J26" t="str">
+        <x:v>challenge</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Level.xlsx
+++ b/design/tables/Level.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="R617ff920f02345aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="R6d5a41ff2a5b4ee4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -353,11 +353,9 @@
         <x:v>怪物移速倍率</x:v>
       </x:c>
       <x:c r="I1" s="6" t="str">
-        <x:v>可用店员（竖线分隔）</x:v>
-      </x:c>
-      <x:c r="J1" s="12" t="str">
         <x:v>adventure冒险；challenge固定挑战；不计入冒险进度</x:v>
       </x:c>
+      <x:c r="J1" s="12"/>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
@@ -387,9 +385,7 @@
       <x:c r="I2" s="3" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
-        <x:v>client</x:v>
-      </x:c>
+      <x:c r="J2" s="12"/>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -419,9 +415,7 @@
       <x:c r="I3" s="3" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="J3" s="12" t="str">
-        <x:v>string</x:v>
-      </x:c>
+      <x:c r="J3" s="12"/>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -449,11 +443,9 @@
         <x:v>怪物移速倍率</x:v>
       </x:c>
       <x:c r="I4" s="6" t="str">
-        <x:v>可用店员（竖线分隔）</x:v>
-      </x:c>
-      <x:c r="J4" s="12" t="str">
         <x:v>模式</x:v>
       </x:c>
+      <x:c r="J4" s="12"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -481,11 +473,9 @@
         <x:v>enemySpeedScale</x:v>
       </x:c>
       <x:c r="I5" s="5" t="str">
-        <x:v>availableTowers</x:v>
-      </x:c>
-      <x:c r="J5" s="14" t="str">
         <x:v>mode</x:v>
       </x:c>
+      <x:c r="J5" s="14"/>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="n">
@@ -511,11 +501,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="2" t="str">
-        <x:v>sprout</x:v>
-      </x:c>
-      <x:c r="J6" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J6"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="7" t="n">
@@ -541,11 +529,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I7" s="2" t="str">
-        <x:v>sprout|frost</x:v>
-      </x:c>
-      <x:c r="J7" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J7"/>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="7" t="n">
@@ -571,11 +557,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I8" s="2" t="str">
-        <x:v>sprout|frost|bloom</x:v>
-      </x:c>
-      <x:c r="J8" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J8"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="7" t="n">
@@ -601,11 +585,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I9" s="2" t="str">
-        <x:v>sprout|frost|bloom</x:v>
-      </x:c>
-      <x:c r="J9" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J9"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="7" t="n">
@@ -633,11 +615,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I10" s="2" t="str">
-        <x:v>sprout|frost|bloom</x:v>
-      </x:c>
-      <x:c r="J10" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J10"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="7" t="n">
@@ -665,11 +645,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="2" t="str">
-        <x:v>sprout|frost|bloom|scope</x:v>
-      </x:c>
-      <x:c r="J11" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J11"/>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="7" t="n">
@@ -697,11 +675,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="2" t="str">
-        <x:v>sprout|frost|bloom|scope</x:v>
-      </x:c>
-      <x:c r="J12" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J12"/>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="7" t="n">
@@ -729,11 +705,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I13" s="2" t="str">
-        <x:v>scope|frost|bloom|spark</x:v>
-      </x:c>
-      <x:c r="J13" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J13"/>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="7" t="n">
@@ -761,11 +735,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="2" t="str">
-        <x:v>scope|frost|bloom|spark</x:v>
-      </x:c>
-      <x:c r="J14" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J14"/>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="7" t="n">
@@ -793,11 +765,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="2" t="str">
-        <x:v>scope|frost|bloom|spark</x:v>
-      </x:c>
-      <x:c r="J15" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J15"/>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="7" t="n">
@@ -825,11 +795,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="2" t="str">
-        <x:v>sprout|frost|bloom|ember</x:v>
-      </x:c>
-      <x:c r="J16" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J16"/>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="7" t="n">
@@ -857,11 +825,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I17" s="2" t="str">
-        <x:v>scope|frost|bloom|ember</x:v>
-      </x:c>
-      <x:c r="J17" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J17"/>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="7" t="n">
@@ -889,11 +855,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I18" s="2" t="str">
-        <x:v>sprout|bloom|mint|ember</x:v>
-      </x:c>
-      <x:c r="J18" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J18"/>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="7" t="n">
@@ -921,11 +885,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="2" t="str">
-        <x:v>scope|spark|mint|frost</x:v>
-      </x:c>
-      <x:c r="J19" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J19"/>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="7" t="n">
@@ -953,11 +915,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="2" t="str">
-        <x:v>scope|bloom|ember|mint</x:v>
-      </x:c>
-      <x:c r="J20" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J20"/>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="7" t="n">
@@ -985,11 +945,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="2" t="str">
-        <x:v>sprout|frost|bloom|fan</x:v>
-      </x:c>
-      <x:c r="J21" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J21"/>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="7" t="n">
@@ -1017,11 +975,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="2" t="str">
-        <x:v>scope|spark|frost|fan</x:v>
-      </x:c>
-      <x:c r="J22" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J22"/>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="7" t="n">
@@ -1049,11 +1005,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="2" t="str">
-        <x:v>scope|bloom|mint|fan</x:v>
-      </x:c>
-      <x:c r="J23" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J23"/>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="7" t="n">
@@ -1081,11 +1035,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="2" t="str">
-        <x:v>scope|frost|ember|fan</x:v>
-      </x:c>
-      <x:c r="J24" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J24"/>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="7" t="n">
@@ -1113,11 +1065,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I25" s="2" t="str">
-        <x:v>scope|frost|bloom|mint</x:v>
-      </x:c>
-      <x:c r="J25" t="str">
-        <x:v>adventure</x:v>
-      </x:c>
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="n">
@@ -1145,11 +1095,9 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I26" t="str">
-        <x:v>frost|bloom|scope|mint</x:v>
-      </x:c>
-      <x:c r="J26" t="str">
         <x:v>challenge</x:v>
       </x:c>
+      <x:c r="J26"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/tables/Level.xlsx
+++ b/design/tables/Level.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="R6d5a41ff2a5b4ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="Rc8b15a51fb2b4738"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1083,13 +1083,13 @@
         <x:v>challenge.goal</x:v>
       </x:c>
       <x:c r="E26" t="n">
-        <x:v>410</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="F26" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G26" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H26" t="n">
         <x:v>1</x:v>

--- a/design/tables/Level.xlsx
+++ b/design/tables/Level.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="Rc8b15a51fb2b4738"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="R26fd68cfeec045f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -503,7 +503,7 @@
       <x:c r="I6" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J6"/>
+      <x:c r="J6" t="str"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="7" t="n">
@@ -531,7 +531,7 @@
       <x:c r="I7" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J7"/>
+      <x:c r="J7" t="str"/>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="7" t="n">
@@ -559,7 +559,7 @@
       <x:c r="I8" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J8"/>
+      <x:c r="J8" t="str"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="7" t="n">
@@ -587,7 +587,7 @@
       <x:c r="I9" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J9"/>
+      <x:c r="J9" t="str"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="7" t="n">
@@ -617,7 +617,7 @@
       <x:c r="I10" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J10"/>
+      <x:c r="J10" t="str"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="7" t="n">
@@ -647,7 +647,7 @@
       <x:c r="I11" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J11"/>
+      <x:c r="J11" t="str"/>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="7" t="n">
@@ -677,7 +677,7 @@
       <x:c r="I12" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J12"/>
+      <x:c r="J12" t="str"/>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="7" t="n">
@@ -707,7 +707,7 @@
       <x:c r="I13" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J13"/>
+      <x:c r="J13" t="str"/>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="7" t="n">
@@ -737,7 +737,7 @@
       <x:c r="I14" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J14"/>
+      <x:c r="J14" t="str"/>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="7" t="n">
@@ -767,7 +767,7 @@
       <x:c r="I15" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J15"/>
+      <x:c r="J15" t="str"/>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="7" t="n">
@@ -797,7 +797,7 @@
       <x:c r="I16" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J16"/>
+      <x:c r="J16" t="str"/>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="7" t="n">
@@ -827,7 +827,7 @@
       <x:c r="I17" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J17"/>
+      <x:c r="J17" t="str"/>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="7" t="n">
@@ -857,7 +857,7 @@
       <x:c r="I18" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J18"/>
+      <x:c r="J18" t="str"/>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="7" t="n">
@@ -887,7 +887,7 @@
       <x:c r="I19" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J19"/>
+      <x:c r="J19" t="str"/>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="7" t="n">
@@ -917,7 +917,7 @@
       <x:c r="I20" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J20"/>
+      <x:c r="J20" t="str"/>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="7" t="n">
@@ -947,7 +947,7 @@
       <x:c r="I21" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J21"/>
+      <x:c r="J21" t="str"/>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="7" t="n">
@@ -977,7 +977,7 @@
       <x:c r="I22" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J22"/>
+      <x:c r="J22" t="str"/>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="7" t="n">
@@ -1007,7 +1007,7 @@
       <x:c r="I23" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J23"/>
+      <x:c r="J23" t="str"/>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="7" t="n">
@@ -1037,7 +1037,7 @@
       <x:c r="I24" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J24"/>
+      <x:c r="J24" t="str"/>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="7" t="n">
@@ -1067,7 +1067,7 @@
       <x:c r="I25" s="2" t="str">
         <x:v>adventure</x:v>
       </x:c>
-      <x:c r="J25"/>
+      <x:c r="J25" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="n">
@@ -1077,10 +1077,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>challenge.title</x:v>
+        <x:v>topics.opening.title</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>challenge.goal</x:v>
+        <x:v>topics.opening.rule</x:v>
       </x:c>
       <x:c r="E26" t="n">
         <x:v>350</x:v>
@@ -1097,7 +1097,157 @@
       <x:c r="I26" t="str">
         <x:v>challenge</x:v>
       </x:c>
-      <x:c r="J26"/>
+      <x:c r="J26" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B27" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>topics.express.title</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>topics.express.rule</x:v>
+      </x:c>
+      <x:c r="E27" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="F27" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>challenge</x:v>
+      </x:c>
+      <x:c r="J27" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B28" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>topics.warehouse.title</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>topics.warehouse.rule</x:v>
+      </x:c>
+      <x:c r="E28" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="F28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>challenge</x:v>
+      </x:c>
+      <x:c r="J28" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>topics.coins.title</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>topics.coins.rule</x:v>
+      </x:c>
+      <x:c r="E29" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="F29" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>challenge</x:v>
+      </x:c>
+      <x:c r="J29" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B30" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>topics.mini.title</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>topics.mini.rule</x:v>
+      </x:c>
+      <x:c r="E30" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="F30" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>challenge</x:v>
+      </x:c>
+      <x:c r="J30" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>topics.midnight.title</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>topics.midnight.rule</x:v>
+      </x:c>
+      <x:c r="E31" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="F31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>challenge</x:v>
+      </x:c>
+      <x:c r="J31" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/tables/Level.xlsx
+++ b/design/tables/Level.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="R26fd68cfeec045f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="Rd65dda33a8a34730"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1083,7 +1083,7 @@
         <x:v>topics.opening.rule</x:v>
       </x:c>
       <x:c r="E26" t="n">
-        <x:v>350</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="F26" t="n">
         <x:v>10</x:v>
@@ -1113,7 +1113,7 @@
         <x:v>topics.express.rule</x:v>
       </x:c>
       <x:c r="E27" t="n">
-        <x:v>350</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="F27" t="n">
         <x:v>10</x:v>
@@ -1143,7 +1143,7 @@
         <x:v>topics.warehouse.rule</x:v>
       </x:c>
       <x:c r="E28" t="n">
-        <x:v>350</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="F28" t="n">
         <x:v>10</x:v>
@@ -1173,7 +1173,7 @@
         <x:v>topics.coins.rule</x:v>
       </x:c>
       <x:c r="E29" t="n">
-        <x:v>350</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="F29" t="n">
         <x:v>10</x:v>
@@ -1203,7 +1203,7 @@
         <x:v>topics.mini.rule</x:v>
       </x:c>
       <x:c r="E30" t="n">
-        <x:v>350</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="F30" t="n">
         <x:v>10</x:v>
@@ -1233,7 +1233,7 @@
         <x:v>topics.midnight.rule</x:v>
       </x:c>
       <x:c r="E31" t="n">
-        <x:v>400</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="F31" t="n">
         <x:v>10</x:v>

--- a/design/tables/Level.xlsx
+++ b/design/tables/Level.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="Rd65dda33a8a34730"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="Rd755fa9309584477"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -495,7 +495,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G6" s="8" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.825</x:v>
       </x:c>
       <x:c r="H6" s="8" t="n">
         <x:v>1</x:v>
@@ -523,7 +523,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G7" s="8" t="n">
-        <x:v>0.7</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="H7" s="8" t="n">
         <x:v>1</x:v>
@@ -551,7 +551,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G8" s="8" t="n">
-        <x:v>0.82</x:v>
+        <x:v>1.23</x:v>
       </x:c>
       <x:c r="H8" s="8" t="n">
         <x:v>1</x:v>
@@ -579,7 +579,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G9" s="8" t="n">
-        <x:v>1.12</x:v>
+        <x:v>1.68</x:v>
       </x:c>
       <x:c r="H9" s="8" t="n">
         <x:v>1</x:v>
@@ -609,7 +609,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G10" s="8" t="n">
-        <x:v>1.16</x:v>
+        <x:v>1.74</x:v>
       </x:c>
       <x:c r="H10" s="8" t="n">
         <x:v>1</x:v>
@@ -639,7 +639,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G11" s="8" t="n">
-        <x:v>1.24</x:v>
+        <x:v>1.86</x:v>
       </x:c>
       <x:c r="H11" s="8" t="n">
         <x:v>1</x:v>
@@ -669,7 +669,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G12" s="8" t="n">
-        <x:v>1.3</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="H12" s="8" t="n">
         <x:v>1</x:v>
@@ -699,7 +699,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G13" s="8" t="n">
-        <x:v>1.38</x:v>
+        <x:v>2.07</x:v>
       </x:c>
       <x:c r="H13" s="8" t="n">
         <x:v>1</x:v>
@@ -729,7 +729,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G14" s="8" t="n">
-        <x:v>1.46</x:v>
+        <x:v>2.19</x:v>
       </x:c>
       <x:c r="H14" s="8" t="n">
         <x:v>1</x:v>
@@ -759,7 +759,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G15" s="8" t="n">
-        <x:v>1.54</x:v>
+        <x:v>2.31</x:v>
       </x:c>
       <x:c r="H15" s="8" t="n">
         <x:v>1</x:v>
@@ -789,7 +789,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G16" s="8" t="n">
-        <x:v>1.48</x:v>
+        <x:v>2.22</x:v>
       </x:c>
       <x:c r="H16" s="8" t="n">
         <x:v>1</x:v>
@@ -819,7 +819,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G17" s="8" t="n">
-        <x:v>1.525</x:v>
+        <x:v>2.2875</x:v>
       </x:c>
       <x:c r="H17" s="8" t="n">
         <x:v>1</x:v>
@@ -849,7 +849,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G18" s="8" t="n">
-        <x:v>1.57</x:v>
+        <x:v>2.355</x:v>
       </x:c>
       <x:c r="H18" s="8" t="n">
         <x:v>1</x:v>
@@ -879,7 +879,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G19" s="8" t="n">
-        <x:v>1.615</x:v>
+        <x:v>2.4225</x:v>
       </x:c>
       <x:c r="H19" s="8" t="n">
         <x:v>1</x:v>
@@ -909,7 +909,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G20" s="8" t="n">
-        <x:v>1.66</x:v>
+        <x:v>2.49</x:v>
       </x:c>
       <x:c r="H20" s="8" t="n">
         <x:v>1</x:v>
@@ -939,7 +939,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G21" s="8" t="n">
-        <x:v>1.705</x:v>
+        <x:v>2.5575</x:v>
       </x:c>
       <x:c r="H21" s="8" t="n">
         <x:v>1</x:v>
@@ -969,7 +969,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G22" s="8" t="n">
-        <x:v>1.75</x:v>
+        <x:v>2.625</x:v>
       </x:c>
       <x:c r="H22" s="8" t="n">
         <x:v>1</x:v>
@@ -999,7 +999,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G23" s="8" t="n">
-        <x:v>1.795</x:v>
+        <x:v>2.6925</x:v>
       </x:c>
       <x:c r="H23" s="8" t="n">
         <x:v>1</x:v>
@@ -1029,7 +1029,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G24" s="8" t="n">
-        <x:v>1.84</x:v>
+        <x:v>2.76</x:v>
       </x:c>
       <x:c r="H24" s="8" t="n">
         <x:v>1</x:v>
@@ -1059,7 +1059,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G25" s="8" t="n">
-        <x:v>1.885</x:v>
+        <x:v>2.8275</x:v>
       </x:c>
       <x:c r="H25" s="8" t="n">
         <x:v>1</x:v>

--- a/design/tables/Level.xlsx
+++ b/design/tables/Level.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="Rd755fa9309584477"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level" sheetId="1" r:id="Ra977a717f8604edd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1071,7 +1071,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="n">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B26" t="n">
         <x:v>21</x:v>
@@ -1101,7 +1101,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="n">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B27" t="n">
         <x:v>6</x:v>
@@ -1131,7 +1131,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="n">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B28" t="n">
         <x:v>9</x:v>
@@ -1161,7 +1161,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="n">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B29" t="n">
         <x:v>13</x:v>
@@ -1191,7 +1191,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B30" t="n">
         <x:v>18</x:v>
@@ -1221,7 +1221,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="n">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B31" t="n">
         <x:v>20</x:v>
@@ -1248,6 +1248,426 @@
         <x:v>challenge</x:v>
       </x:c>
       <x:c r="J31" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B32" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C32" s="2" t="str">
+        <x:v>level.21.title</x:v>
+      </x:c>
+      <x:c r="D32" s="2" t="str">
+        <x:v>level.21.goal</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="n">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="F32" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G32" s="8" t="n">
+        <x:v>2.91233</x:v>
+      </x:c>
+      <x:c r="H32" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I32" s="2" t="str">
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J32" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B33" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C33" s="2" t="str">
+        <x:v>level.22.title</x:v>
+      </x:c>
+      <x:c r="D33" s="2" t="str">
+        <x:v>level.22.goal</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="n">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="F33" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G33" s="8" t="n">
+        <x:v>2.99715</x:v>
+      </x:c>
+      <x:c r="H33" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I33" s="2" t="str">
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J33" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B34" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C34" s="2" t="str">
+        <x:v>level.23.title</x:v>
+      </x:c>
+      <x:c r="D34" s="2" t="str">
+        <x:v>level.23.goal</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="n">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="F34" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G34" s="8" t="n">
+        <x:v>3.08198</x:v>
+      </x:c>
+      <x:c r="H34" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I34" s="2" t="str">
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J34" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B35" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C35" s="2" t="str">
+        <x:v>level.24.title</x:v>
+      </x:c>
+      <x:c r="D35" s="2" t="str">
+        <x:v>level.24.goal</x:v>
+      </x:c>
+      <x:c r="E35" s="7" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="F35" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G35" s="8" t="n">
+        <x:v>3.1668</x:v>
+      </x:c>
+      <x:c r="H35" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I35" s="2" t="str">
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J35" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B36" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C36" s="2" t="str">
+        <x:v>level.25.title</x:v>
+      </x:c>
+      <x:c r="D36" s="2" t="str">
+        <x:v>level.25.goal</x:v>
+      </x:c>
+      <x:c r="E36" s="7" t="n">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="F36" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G36" s="8" t="n">
+        <x:v>3.25162</x:v>
+      </x:c>
+      <x:c r="H36" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I36" s="2" t="str">
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J36" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B37" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C37" s="2" t="str">
+        <x:v>level.26.title</x:v>
+      </x:c>
+      <x:c r="D37" s="2" t="str">
+        <x:v>level.26.goal</x:v>
+      </x:c>
+      <x:c r="E37" s="7" t="n">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="F37" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G37" s="8" t="n">
+        <x:v>3.33645</x:v>
+      </x:c>
+      <x:c r="H37" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I37" s="2" t="str">
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J37" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B38" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C38" s="2" t="str">
+        <x:v>level.27.title</x:v>
+      </x:c>
+      <x:c r="D38" s="2" t="str">
+        <x:v>level.27.goal</x:v>
+      </x:c>
+      <x:c r="E38" s="7" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="F38" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G38" s="8" t="n">
+        <x:v>3.42128</x:v>
+      </x:c>
+      <x:c r="H38" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I38" s="2" t="str">
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J38" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B39" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C39" s="2" t="str">
+        <x:v>level.28.title</x:v>
+      </x:c>
+      <x:c r="D39" s="2" t="str">
+        <x:v>level.28.goal</x:v>
+      </x:c>
+      <x:c r="E39" s="7" t="n">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="F39" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G39" s="8" t="n">
+        <x:v>3.5061</x:v>
+      </x:c>
+      <x:c r="H39" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I39" s="2" t="str">
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J39" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B40" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C40" s="2" t="str">
+        <x:v>level.29.title</x:v>
+      </x:c>
+      <x:c r="D40" s="2" t="str">
+        <x:v>level.29.goal</x:v>
+      </x:c>
+      <x:c r="E40" s="7" t="n">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="F40" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G40" s="8" t="n">
+        <x:v>3.59093</x:v>
+      </x:c>
+      <x:c r="H40" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I40" s="2" t="str">
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J40" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B41" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C41" s="2" t="str">
+        <x:v>level.30.title</x:v>
+      </x:c>
+      <x:c r="D41" s="2" t="str">
+        <x:v>level.30.goal</x:v>
+      </x:c>
+      <x:c r="E41" s="7" t="n">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="F41" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G41" s="8" t="n">
+        <x:v>3.67575</x:v>
+      </x:c>
+      <x:c r="H41" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I41" s="2" t="str">
+        <x:v>adventure</x:v>
+      </x:c>
+      <x:c r="J41" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="7" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B42" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C42" s="2" t="str">
+        <x:v>topics.freezer.title</x:v>
+      </x:c>
+      <x:c r="D42" s="2" t="str">
+        <x:v>topics.freezer.rule</x:v>
+      </x:c>
+      <x:c r="E42" s="7" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="F42" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G42" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H42" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I42" s="2" t="str">
+        <x:v>challenge</x:v>
+      </x:c>
+      <x:c r="J42" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="7" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B43" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C43" s="2" t="str">
+        <x:v>topics.gifts.title</x:v>
+      </x:c>
+      <x:c r="D43" s="2" t="str">
+        <x:v>topics.gifts.rule</x:v>
+      </x:c>
+      <x:c r="E43" s="7" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="F43" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G43" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H43" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I43" s="2" t="str">
+        <x:v>challenge</x:v>
+      </x:c>
+      <x:c r="J43" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="7" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B44" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C44" s="2" t="str">
+        <x:v>topics.storm.title</x:v>
+      </x:c>
+      <x:c r="D44" s="2" t="str">
+        <x:v>topics.storm.rule</x:v>
+      </x:c>
+      <x:c r="E44" s="7" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="F44" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G44" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H44" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I44" s="2" t="str">
+        <x:v>challenge</x:v>
+      </x:c>
+      <x:c r="J44" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="7" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B45" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C45" s="2" t="str">
+        <x:v>topics.dawn.title</x:v>
+      </x:c>
+      <x:c r="D45" s="2" t="str">
+        <x:v>topics.dawn.rule</x:v>
+      </x:c>
+      <x:c r="E45" s="7" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="F45" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G45" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H45" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I45" s="2" t="str">
+        <x:v>challenge</x:v>
+      </x:c>
+      <x:c r="J45" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
